--- a/data/trans_camb/IP12-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP12-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 11,11</t>
+          <t>-1,5; 10,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 13,09</t>
+          <t>0,06; 13,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 11,22</t>
+          <t>-0,57; 11,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 4,2</t>
+          <t>-8,89; 4,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,63; -0,03</t>
+          <t>-11,19; -0,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 0,5</t>
+          <t>-11,0; 0,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 5,61</t>
+          <t>-3,15; 5,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 3,98</t>
+          <t>-4,18; 4,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 3,98</t>
+          <t>-4,37; 3,81</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-28,34; 347,92</t>
+          <t>-27,52; 321,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 409,65</t>
+          <t>-3,95; 426,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-19,11; 409,2</t>
+          <t>-14,94; 345,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-69,6; 75,43</t>
+          <t>-70,27; 76,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-87,33; 9,82</t>
+          <t>-87,4; -0,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-81,96; 29,22</t>
+          <t>-82,39; 23,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,46; 105,8</t>
+          <t>-35,7; 100,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-48,41; 72,75</t>
+          <t>-44,92; 88,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-48,17; 69,57</t>
+          <t>-47,23; 67,74</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 12,76</t>
+          <t>-1,65; 12,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 2,15</t>
+          <t>-8,75; 2,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 2,67</t>
+          <t>-8,79; 2,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 4,41</t>
+          <t>-7,47; 4,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 6,91</t>
+          <t>-5,52; 6,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 11,27</t>
+          <t>-2,84; 11,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 6,6</t>
+          <t>-2,81; 6,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 2,56</t>
+          <t>-5,07; 2,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 5,14</t>
+          <t>-4,15; 5,03</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-21,34; 273,25</t>
+          <t>-22,34; 285,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-78,55; 57,59</t>
+          <t>-78,96; 74,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-79,78; 70,83</t>
+          <t>-80,94; 69,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-71,17; 110,21</t>
+          <t>-74,53; 126,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,55; 188,17</t>
+          <t>-53,72; 172,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,37; 261,41</t>
+          <t>-31,85; 325,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-27,78; 129,68</t>
+          <t>-31,85; 121,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-55,8; 52,55</t>
+          <t>-52,78; 60,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-40,19; 98,6</t>
+          <t>-44,2; 101,95</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 9,2</t>
+          <t>-4,3; 9,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 8,42</t>
+          <t>-6,27; 7,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 6,54</t>
+          <t>-7,57; 6,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 9,13</t>
+          <t>-4,37; 9,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 6,71</t>
+          <t>-6,55; 7,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 8,16</t>
+          <t>-5,5; 8,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 6,65</t>
+          <t>-2,53; 6,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 5,25</t>
+          <t>-4,81; 5,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 5,46</t>
+          <t>-4,88; 5,12</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-51,99; 281,01</t>
+          <t>-49,93; 274,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-64,7; 253,6</t>
+          <t>-65,05; 252,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-76,02; 197,65</t>
+          <t>-75,54; 197,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-43,71; 237,04</t>
+          <t>-44,82; 235,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-66,48; 162,68</t>
+          <t>-69,99; 174,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,62; 208,49</t>
+          <t>-60,54; 191,08</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,14; 138,96</t>
+          <t>-30,22; 152,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-48,8; 108,65</t>
+          <t>-55,8; 113,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-51,63; 127,57</t>
+          <t>-54,85; 109,93</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 5,89</t>
+          <t>-3,03; 5,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 6,52</t>
+          <t>-1,74; 6,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 0,94</t>
+          <t>-6,0; 1,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 6,84</t>
+          <t>-2,15; 6,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 5,08</t>
+          <t>-3,14; 5,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 3,43</t>
+          <t>-4,94; 3,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 5,02</t>
+          <t>-1,25; 5,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 4,52</t>
+          <t>-1,29; 4,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 1,21</t>
+          <t>-4,39; 1,3</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-33,16; 119,44</t>
+          <t>-33,21; 121,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-20,04; 135,99</t>
+          <t>-21,08; 123,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-69,97; 23,35</t>
+          <t>-68,64; 31,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-25,42; 130,38</t>
+          <t>-23,99; 125,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-34,06; 96,58</t>
+          <t>-35,28; 103,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-51,39; 66,72</t>
+          <t>-51,24; 68,32</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-13,14; 87,91</t>
+          <t>-15,49; 88,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-17,91; 78,21</t>
+          <t>-16,06; 78,4</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-50,62; 20,66</t>
+          <t>-51,25; 24,01</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 5,48</t>
+          <t>-6,69; 5,4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 5,26</t>
+          <t>-6,33; 5,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 9,7</t>
+          <t>-3,31; 9,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 6,41</t>
+          <t>-2,62; 6,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 4,8</t>
+          <t>-4,03; 4,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 11,55</t>
+          <t>0,09; 10,98</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 5,23</t>
+          <t>-2,01; 5,17</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 3,88</t>
+          <t>-3,06; 3,78</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 8,72</t>
+          <t>0,13; 8,58</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-53,61; 120,02</t>
+          <t>-56,46; 109,92</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-56,62; 127,14</t>
+          <t>-56,75; 116,23</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-33,11; 218,44</t>
+          <t>-30,12; 195,18</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-40,45; 253,71</t>
+          <t>-43,0; 216,27</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-58,65; 217,08</t>
+          <t>-56,16; 169,98</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-15,84; 398,92</t>
+          <t>-16,0; 378,3</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-30,03; 119,28</t>
+          <t>-25,48; 134,13</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-43,19; 98,06</t>
+          <t>-39,53; 85,94</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 192,66</t>
+          <t>0,21; 191,98</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 7,92</t>
+          <t>-3,66; 8,47</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 7,91</t>
+          <t>-3,69; 7,92</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 8,58</t>
+          <t>-2,53; 9,1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 10,83</t>
+          <t>-3,21; 10,69</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 6,81</t>
+          <t>-5,82; 7,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 7,8</t>
+          <t>-5,36; 7,97</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 8,23</t>
+          <t>-1,38; 8,2</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 5,42</t>
+          <t>-2,73; 5,82</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 5,98</t>
+          <t>-2,29; 6,63</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 680,17</t>
+          <t>-78,82; 692,34</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-80,32; 674,36</t>
+          <t>-76,47; 582,59</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-58,01; 704,76</t>
+          <t>-55,49; 606,43</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-51,36; 432,51</t>
+          <t>-45,5; 370,11</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-73,37; 287,79</t>
+          <t>-74,13; 297,53</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-74,27; 333,27</t>
+          <t>-74,83; 297,43</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-33,59; 316,37</t>
+          <t>-24,67; 330,98</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-52,16; 226,5</t>
+          <t>-45,46; 227,98</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-40,89; 245,31</t>
+          <t>-41,04; 264,6</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,05; 4,78</t>
+          <t>0,09; 5,1</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 3,86</t>
+          <t>-0,79; 3,81</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 2,68</t>
+          <t>-1,65; 3,19</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 3,66</t>
+          <t>-1,13; 3,58</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 1,72</t>
+          <t>-2,76; 1,75</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 2,86</t>
+          <t>-1,55; 3,06</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,62</t>
+          <t>0,09; 3,39</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 2,2</t>
+          <t>-1,15; 2,0</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 2,3</t>
+          <t>-1,0; 2,3</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 87,31</t>
+          <t>1,38; 97,15</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 73,0</t>
+          <t>-10,15; 72,99</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-24,23; 50,21</t>
+          <t>-21,0; 61,44</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-15,5; 61,7</t>
+          <t>-15,04; 59,43</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-33,32; 30,02</t>
+          <t>-33,93; 30,25</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-21,96; 48,46</t>
+          <t>-19,95; 52,09</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,93; 64,34</t>
+          <t>1,07; 56,3</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 35,72</t>
+          <t>-15,42; 34,43</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-15,32; 38,95</t>
+          <t>-13,47; 38,32</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP12-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP12-Clase-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolores o síntomas</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolores o síntomas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 10,76</t>
+          <t>-2,47; 10,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 13,05</t>
+          <t>0,02; 13,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 11,58</t>
+          <t>-0,77; 11,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 4,56</t>
+          <t>-8,55; 4,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,19; -0,32</t>
+          <t>-11,91; -0,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 0,67</t>
+          <t>-11,0; 0,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 5,66</t>
+          <t>-3,4; 5,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 4,57</t>
+          <t>-4,32; 4,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 3,81</t>
+          <t>-4,19; 3,85</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-27,52; 321,41</t>
+          <t>-36,24; 334,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 426,08</t>
+          <t>-1,23; 454,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 345,24</t>
+          <t>-13,49; 372,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-70,27; 76,43</t>
+          <t>-69,51; 98,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-87,4; -0,57</t>
+          <t>-86,35; 10,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-82,39; 23,21</t>
+          <t>-83,34; 22,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-35,7; 100,23</t>
+          <t>-38,66; 99,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-44,92; 88,08</t>
+          <t>-47,21; 80,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-47,23; 67,74</t>
+          <t>-44,58; 75,7</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 12,52</t>
+          <t>-0,93; 13,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 2,83</t>
+          <t>-8,51; 2,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 2,12</t>
+          <t>-8,63; 2,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 4,53</t>
+          <t>-7,22; 4,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 6,6</t>
+          <t>-5,07; 6,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 11,66</t>
+          <t>-3,38; 11,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 6,53</t>
+          <t>-2,67; 6,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 2,87</t>
+          <t>-5,07; 3,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 5,03</t>
+          <t>-4,09; 5,49</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-22,34; 285,45</t>
+          <t>-13,87; 309,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-78,96; 74,54</t>
+          <t>-78,25; 70,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-80,94; 69,14</t>
+          <t>-79,08; 68,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-74,53; 126,68</t>
+          <t>-69,99; 140,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-53,72; 172,94</t>
+          <t>-52,26; 191,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,85; 325,87</t>
+          <t>-40,62; 301,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,85; 121,67</t>
+          <t>-27,83; 138,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-52,78; 60,89</t>
+          <t>-53,85; 62,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-44,2; 101,95</t>
+          <t>-44,07; 110,42</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 9,5</t>
+          <t>-4,45; 9,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 7,53</t>
+          <t>-5,96; 9,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 6,63</t>
+          <t>-6,89; 6,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 9,04</t>
+          <t>-3,64; 8,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 7,0</t>
+          <t>-5,78; 6,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 8,41</t>
+          <t>-6,27; 8,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 6,77</t>
+          <t>-2,11; 7,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 5,08</t>
+          <t>-3,75; 5,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 5,12</t>
+          <t>-4,34; 5,51</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-49,93; 274,97</t>
+          <t>-49,51; 389,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-65,05; 252,25</t>
+          <t>-69,18; 328,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-75,54; 197,37</t>
+          <t>-72,75; 246,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-44,82; 235,24</t>
+          <t>-42,26; 202,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-69,99; 174,07</t>
+          <t>-66,22; 177,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-60,54; 191,08</t>
+          <t>-66,3; 212,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-30,22; 152,42</t>
+          <t>-24,68; 169,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-55,8; 113,39</t>
+          <t>-45,96; 116,55</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-54,85; 109,93</t>
+          <t>-54,81; 110,24</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 5,92</t>
+          <t>-2,51; 5,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 6,39</t>
+          <t>-1,84; 6,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 1,42</t>
+          <t>-6,12; 1,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 6,97</t>
+          <t>-1,83; 6,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 5,34</t>
+          <t>-3,29; 5,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 3,63</t>
+          <t>-5,13; 3,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 5,13</t>
+          <t>-1,33; 5,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 4,47</t>
+          <t>-1,28; 4,88</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 1,3</t>
+          <t>-4,43; 1,21</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-33,21; 121,57</t>
+          <t>-33,27; 126,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-21,08; 123,15</t>
+          <t>-22,77; 125,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-68,64; 31,26</t>
+          <t>-70,91; 26,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-23,99; 125,26</t>
+          <t>-19,3; 128,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-35,28; 103,91</t>
+          <t>-33,99; 89,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-51,24; 68,32</t>
+          <t>-50,59; 64,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-15,49; 88,74</t>
+          <t>-15,89; 85,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 78,4</t>
+          <t>-16,22; 82,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-51,25; 24,01</t>
+          <t>-52,1; 20,39</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 5,4</t>
+          <t>-5,95; 6,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 5,41</t>
+          <t>-6,29; 5,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 9,34</t>
+          <t>-2,86; 9,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 6,2</t>
+          <t>-2,71; 6,6</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 4,48</t>
+          <t>-3,69; 4,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,09; 10,98</t>
+          <t>-0,15; 10,91</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 5,17</t>
+          <t>-2,53; 4,98</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 3,78</t>
+          <t>-3,49; 3,5</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,13; 8,58</t>
+          <t>-0,17; 8,45</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-56,46; 109,92</t>
+          <t>-51,59; 134,99</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-56,75; 116,23</t>
+          <t>-55,92; 132,82</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-30,12; 195,18</t>
+          <t>-30,23; 218,64</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-43,0; 216,27</t>
+          <t>-41,59; 245,82</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-56,16; 169,98</t>
+          <t>-57,13; 178,45</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-16,0; 378,3</t>
+          <t>-6,52; 400,18</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-25,48; 134,13</t>
+          <t>-31,62; 112,15</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-39,53; 85,94</t>
+          <t>-43,14; 81,85</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,21; 191,98</t>
+          <t>-4,79; 204,88</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 8,47</t>
+          <t>-3,62; 9,13</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 7,92</t>
+          <t>-3,03; 8,45</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 9,1</t>
+          <t>-2,77; 8,33</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 10,69</t>
+          <t>-3,15; 10,53</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 7,0</t>
+          <t>-5,43; 6,63</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 7,97</t>
+          <t>-5,77; 7,69</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 8,2</t>
+          <t>-1,59; 7,87</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 5,82</t>
+          <t>-2,72; 5,65</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 6,63</t>
+          <t>-2,27; 6,51</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-78,82; 692,34</t>
+          <t>-81,2; 663,01</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-76,47; 582,59</t>
+          <t>-73,12; 706,43</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-55,49; 606,43</t>
+          <t>-54,88; 490,62</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-45,5; 370,11</t>
+          <t>-45,18; 443,54</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-74,13; 297,53</t>
+          <t>-78,34; 266,66</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-74,83; 297,43</t>
+          <t>-69,47; 288,07</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-24,67; 330,98</t>
+          <t>-33,58; 271,39</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-45,46; 227,98</t>
+          <t>-47,18; 241,15</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-41,04; 264,6</t>
+          <t>-42,57; 245,68</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,09; 5,1</t>
+          <t>-0,07; 4,84</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 3,81</t>
+          <t>-0,8; 3,63</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 3,19</t>
+          <t>-1,79; 2,9</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 3,58</t>
+          <t>-1,24; 3,51</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 1,75</t>
+          <t>-2,68; 1,7</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 3,06</t>
+          <t>-1,64; 3,0</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,09; 3,39</t>
+          <t>0,05; 3,41</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 2,0</t>
+          <t>-1,13; 2,03</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 2,3</t>
+          <t>-1,05; 2,23</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>1,38; 97,15</t>
+          <t>-1,09; 93,22</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 72,99</t>
+          <t>-10,63; 66,76</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-21,0; 61,44</t>
+          <t>-23,31; 53,5</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-15,04; 59,43</t>
+          <t>-15,66; 58,85</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-33,93; 30,25</t>
+          <t>-32,88; 28,84</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-19,95; 52,09</t>
+          <t>-20,85; 50,32</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,07; 56,3</t>
+          <t>0,43; 56,9</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-15,42; 34,43</t>
+          <t>-15,83; 33,8</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-13,47; 38,32</t>
+          <t>-14,18; 36,08</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP12-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP12-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-2,21</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-5,59</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-4,78</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>4,09</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>6,05</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4,95</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-2,21</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-5,59</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-4,95</t>
+          <t>5,47</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,33</t>
+          <t>0,15</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 10,64</t>
+          <t>-8,53; 4,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,02; 13,4</t>
+          <t>-11,63; -0,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 11,96</t>
+          <t>-10,94; 0,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 4,75</t>
+          <t>-1,46; 11,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,91; -0,23</t>
+          <t>-0,14; 13,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 0,44</t>
+          <t>-0,35; 11,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 5,73</t>
+          <t>-3,42; 5,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 4,32</t>
+          <t>-4,53; 3,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 3,85</t>
+          <t>-4,16; 4,54</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-23,06%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-58,35%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-49,9%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>74,2%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>109,84%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>89,8%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-23,06%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-58,35%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-51,72%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-4,35%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-36,24; 334,99</t>
+          <t>-69,6; 75,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 454,37</t>
+          <t>-87,33; 9,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,49; 372,62</t>
+          <t>-81,73; 23,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-69,51; 98,86</t>
+          <t>-28,34; 347,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-86,35; 10,94</t>
+          <t>-11,07; 409,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-83,34; 22,46</t>
+          <t>-14,08; 418,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-38,66; 99,1</t>
+          <t>-37,46; 105,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-47,21; 80,84</t>
+          <t>-48,41; 72,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-44,58; 75,7</t>
+          <t>-42,66; 83,23</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,28</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,7</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4,18</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>5,53</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-2,7</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-2,84</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,28</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,7</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,71</t>
+          <t>-3,2</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,4</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 13,47</t>
+          <t>-7,37; 4,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 2,73</t>
+          <t>-5,49; 6,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 2,7</t>
+          <t>-2,64; 11,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 4,69</t>
+          <t>-1,43; 12,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 6,87</t>
+          <t>-8,3; 2,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 11,31</t>
+          <t>-9,25; 2,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 6,77</t>
+          <t>-2,57; 6,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 3,04</t>
+          <t>-5,4; 2,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 5,49</t>
+          <t>-3,87; 4,88</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-18,12%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9,98%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>59,38%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>73,92%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-36,14%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-37,93%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-18,12%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,98%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>-42,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,87; 309,1</t>
+          <t>-71,17; 110,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-78,25; 70,13</t>
+          <t>-55,55; 188,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-79,08; 68,25</t>
+          <t>-32,17; 284,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-69,99; 140,61</t>
+          <t>-21,34; 273,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,26; 191,95</t>
+          <t>-78,55; 57,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-40,62; 301,38</t>
+          <t>-80,92; 63,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-27,83; 138,7</t>
+          <t>-27,78; 129,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-53,85; 62,99</t>
+          <t>-55,8; 52,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-44,07; 110,42</t>
+          <t>-41,86; 96,23</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,11</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,24</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,47</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>2,29</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,86</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,33</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,11</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,24</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>-0,91</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>-0,23</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 9,96</t>
+          <t>-3,57; 9,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 9,15</t>
+          <t>-5,81; 6,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 6,78</t>
+          <t>-5,68; 8,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 8,47</t>
+          <t>-4,15; 9,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 6,16</t>
+          <t>-5,95; 8,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 8,36</t>
+          <t>-7,28; 5,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 7,46</t>
+          <t>-2,17; 6,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 5,26</t>
+          <t>-4,08; 5,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 5,51</t>
+          <t>-4,62; 5,14</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>30,47%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-3,53%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6,8%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>35,37%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>13,22%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-5,06%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>30,47%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-3,53%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>-14,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>-3,48%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-49,51; 389,48</t>
+          <t>-43,71; 237,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-69,18; 328,92</t>
+          <t>-66,48; 162,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-72,75; 246,86</t>
+          <t>-66,88; 204,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-42,26; 202,44</t>
+          <t>-51,99; 281,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-66,22; 177,02</t>
+          <t>-64,7; 253,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-66,3; 212,43</t>
+          <t>-77,76; 178,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-24,68; 169,48</t>
+          <t>-27,14; 138,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-45,96; 116,55</t>
+          <t>-48,8; 108,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-54,81; 110,24</t>
+          <t>-53,92; 116,32</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,33</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,73</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-0,81</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1,54</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2,3</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-2,43</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,33</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,73</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,7</t>
+          <t>-1,55</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,57</t>
+          <t>-1,14</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 5,85</t>
+          <t>-2,32; 6,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 6,53</t>
+          <t>-3,34; 5,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 1,3</t>
+          <t>-4,75; 3,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 6,92</t>
+          <t>-2,85; 5,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 5,0</t>
+          <t>-1,54; 6,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 3,48</t>
+          <t>-5,91; 2,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 5,02</t>
+          <t>-1,05; 5,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 4,88</t>
+          <t>-1,65; 4,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 1,21</t>
+          <t>-4,11; 1,77</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>30,81%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>9,6%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-10,67%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>22,29%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>33,44%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-35,3%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>30,81%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>9,6%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-9,22%</t>
+          <t>-22,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-21,64%</t>
+          <t>-15,73%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-33,27; 126,84</t>
+          <t>-25,42; 130,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-22,77; 125,54</t>
+          <t>-34,06; 96,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-70,91; 26,07</t>
+          <t>-52,03; 65,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-19,3; 128,19</t>
+          <t>-33,16; 119,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-33,99; 89,29</t>
+          <t>-20,04; 135,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-50,59; 64,74</t>
+          <t>-63,59; 47,03</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-15,89; 85,38</t>
+          <t>-13,14; 87,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-16,22; 82,38</t>
+          <t>-17,91; 78,21</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-52,1; 20,39</t>
+          <t>-46,16; 31,68</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2,09</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,47</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5,18</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,21</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-0,36</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>3,36</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2,09</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,47</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,94</t>
+          <t>2,9</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,19</t>
+          <t>4,15</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 6,33</t>
+          <t>-2,62; 6,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 5,49</t>
+          <t>-3,95; 4,8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 9,81</t>
+          <t>-0,23; 11,91</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 6,6</t>
+          <t>-5,94; 5,48</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 4,79</t>
+          <t>-6,2; 5,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 10,91</t>
+          <t>-3,7; 9,21</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 4,98</t>
+          <t>-2,32; 5,23</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 3,5</t>
+          <t>-3,5; 3,88</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 8,45</t>
+          <t>-0,02; 8,76</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>44,18%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>109,69%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>2,61%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-4,54%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>42,55%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>44,18%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>10,0%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>104,64%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>67,46%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-51,59; 134,99</t>
+          <t>-40,45; 253,71</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-55,92; 132,82</t>
+          <t>-58,65; 217,08</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-30,23; 218,64</t>
+          <t>-15,14; 413,76</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-41,59; 245,82</t>
+          <t>-53,61; 120,02</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-57,13; 178,45</t>
+          <t>-56,62; 127,14</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 400,18</t>
+          <t>-35,48; 208,02</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-31,62; 112,15</t>
+          <t>-30,03; 119,28</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-43,14; 81,85</t>
+          <t>-43,19; 98,06</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 204,88</t>
+          <t>-6,11; 190,61</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>3,38</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0,47</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1,53</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>1,69</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1,88</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>2,74</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>3,38</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>0,47</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,1</t>
+          <t>2,97</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,93</t>
+          <t>2,26</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 9,13</t>
+          <t>-3,32; 10,83</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 8,45</t>
+          <t>-5,46; 6,81</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 8,33</t>
+          <t>-5,2; 8,93</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 10,53</t>
+          <t>-4,25; 7,92</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 6,63</t>
+          <t>-4,59; 7,91</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 7,69</t>
+          <t>-2,63; 8,95</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 7,87</t>
+          <t>-1,52; 8,23</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 5,65</t>
+          <t>-3,09; 5,42</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 6,51</t>
+          <t>-2,0; 6,63</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>64,23%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>8,87%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>29,07%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>45,67%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>50,73%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>74,04%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>64,23%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>8,87%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>50,66%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-81,2; 663,01</t>
+          <t>-51,36; 432,51</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-73,12; 706,43</t>
+          <t>-73,37; 287,79</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-54,88; 490,62</t>
+          <t>-71,33; 377,07</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-45,18; 443,54</t>
+          <t>-100,0; 680,17</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-78,34; 266,66</t>
+          <t>-80,32; 674,36</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-69,47; 288,07</t>
+          <t>-56,6; 742,9</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-33,58; 271,39</t>
+          <t>-33,59; 316,37</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-47,18; 241,15</t>
+          <t>-52,16; 226,5</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-42,57; 245,68</t>
+          <t>-39,43; 256,64</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>1,26</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-0,36</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>0,81</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>2,45</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1,47</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0,52</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>1,26</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-0,36</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,83</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 4,84</t>
+          <t>-1,22; 3,66</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 3,63</t>
+          <t>-2,67; 1,72</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 2,9</t>
+          <t>-1,57; 3,22</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 3,51</t>
+          <t>0,05; 4,78</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 1,7</t>
+          <t>-0,66; 3,86</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 3,0</t>
+          <t>-1,45; 3,01</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,05; 3,41</t>
+          <t>0,24; 3,62</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 2,03</t>
+          <t>-0,87; 2,2</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 2,23</t>
+          <t>-0,89; 2,49</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>18,2%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-5,21%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>11,75%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>37,75%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>22,59%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>8,06%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>18,2%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-5,21%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>12,31%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 93,22</t>
+          <t>-15,5; 61,7</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 66,76</t>
+          <t>-33,32; 30,02</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-23,31; 53,5</t>
+          <t>-19,74; 54,42</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-15,66; 58,85</t>
+          <t>-0,85; 87,31</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-32,88; 28,84</t>
+          <t>-8,93; 73,0</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 50,32</t>
+          <t>-19,59; 55,57</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,43; 56,9</t>
+          <t>2,93; 64,34</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-15,83; 33,8</t>
+          <t>-11,82; 35,72</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-14,18; 36,08</t>
+          <t>-11,66; 43,12</t>
         </is>
       </c>
     </row>
